--- a/Exam/gymtrackerpro/lib/controller/__tests__/it/exercise-controller/listExercises-it-form.xlsx
+++ b/Exam/gymtrackerpro/lib/controller/__tests__/it/exercise-controller/listExercises-it-form.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="78" uniqueCount="49">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="134" uniqueCount="75">
   <si>
     <t>Statement: listExercises(options?: ExerciseListOptions): Promise&lt;ActionResult&lt;PageResult&lt;Exercise&gt;&gt;&gt; - delegates to exerciseService.listExercises() and returns the paginated result wrapped in ActionResult.</t>
   </si>
@@ -82,7 +82,7 @@
     <t>1</t>
   </si>
   <si>
-    <t>Seeded via exerciseService.create(): Squat (active), Bench Press (active). Leg Press seeded then archived via exerciseService.setActive(id, false).</t>
+    <t>Seeded via exerciseService.create(): Squat (LEGS, active), Bench Press (CHEST, active). Leg Press seeded then archived via exerciseService.archiveExercise().</t>
   </si>
   <si>
     <t>listExercises()</t>
@@ -117,6 +117,93 @@
   </si>
   <si>
     <t>{ success: true, data: { items: [], total: 0 } }</t>
+  </si>
+  <si>
+    <t>4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Seeded via exerciseService.create(): Bench Press (CHEST, active). Leg Press seeded then archived via exerciseService.archiveExercise().
+const options: ExerciseListOptions = { includeInactive: true }</t>
+  </si>
+  <si>
+    <t>{ success: true, data: { total: 2, items: [Bench Press, Leg Press] } } — at least one item has isActive = false</t>
+  </si>
+  <si>
+    <t>Not yet run</t>
+  </si>
+  <si>
+    <t>5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Seeded via exerciseService.create(): Bench Press (CHEST), Deadlift (BACK), Cable Row (BACK).
+const options: ExerciseListOptions = { muscleGroup: MuscleGroup.BACK }</t>
+  </si>
+  <si>
+    <t>{ success: true, data: { total: 2, items: all have muscleGroup = BACK } }</t>
+  </si>
+  <si>
+    <t>6</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Seeded via exerciseService.create(): Bench Press (CHEST, BARBELL), Incline Press (CHEST, DUMBBELL), Deadlift (BACK, BARBELL).
+const options: ExerciseListOptions = { search: "PRESS" }</t>
+  </si>
+  <si>
+    <t>{ success: true, data: { total: 2, items: all have name containing "press" (case-insensitive) } }</t>
+  </si>
+  <si>
+    <t>7</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Seeded via exerciseService.create(): Bench Press (CHEST, BARBELL), Incline Press (CHEST, DUMBBELL), Shoulder Press (SHOULDERS, BARBELL).
+const options: ExerciseListOptions = { search: "press", muscleGroup: MuscleGroup.CHEST }</t>
+  </si>
+  <si>
+    <t>{ success: true, data: { total: 2, items: all have muscleGroup = CHEST and name containing "press" } }</t>
+  </si>
+  <si>
+    <t>8</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Seeded via exerciseService.create(): Exercise A (CHEST), Exercise B (CHEST), Exercise C (CHEST).
+const firstOptions: ExerciseListOptions = { page: 1, pageSize: 2 }
+const secondOptions: ExerciseListOptions = { page: 2, pageSize: 2 }</t>
+  </si>
+  <si>
+    <t>listExercises(firstOptions) then listExercises(secondOptions)</t>
+  </si>
+  <si>
+    <t>First call: { success: true, data: { total: 3, items: [2 items] } }. Second call: { success: true, data: { total: 3, items: [1 item] } }. No id appears in both pages.</t>
+  </si>
+  <si>
+    <t>9</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Seeded via exerciseService.create(): Bench Press (CHEST, BARBELL, active), Incline Press (CHEST, DUMBBELL) then archived, Deadlift (BACK, BARBELL, active).
+const options: ExerciseListOptions = { includeInactive: true, search: "press" }</t>
+  </si>
+  <si>
+    <t>{ success: true, data: { total: 2, items: all have name containing "press", at least one has isActive = false } }</t>
+  </si>
+  <si>
+    <t>10</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Seeded via exerciseService.create(): Squat (LEGS, BARBELL), Bench Press (CHEST, BARBELL).
+const options: ExerciseListOptions = { page: 1, pageSize: 100 }</t>
+  </si>
+  <si>
+    <t>{ success: true, data: { total: 2, items: [2 items] } }</t>
+  </si>
+  <si>
+    <t>11</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Seeded via exerciseService.create(): Bench Press (CHEST, BARBELL), Deadlift (BACK, BARBELL).
+const options: ExerciseListOptions = { search: "Bench%" }</t>
+  </si>
+  <si>
+    <t>{ success: true, data: { items: [], total: 0 } } — "%" is treated as a literal character, not a SQL wildcard</t>
   </si>
   <si>
     <t>Testing</t>
@@ -168,7 +255,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <color theme="1"/>
       <family val="2"/>
@@ -186,8 +273,11 @@
     <font>
       <color rgb="FF375623"/>
     </font>
+    <font>
+      <color rgb="FF9C0006"/>
+    </font>
   </fonts>
-  <fills count="6">
+  <fills count="7">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -214,6 +304,11 @@
         <fgColor rgb="FFE2EFDA"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="2">
     <border>
@@ -234,7 +329,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
@@ -252,6 +347,9 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
@@ -798,12 +896,12 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:G4"/>
+  <dimension ref="A1:G12"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="2" width="14" customWidth="1"/>
     <col min="3" max="3" width="80" customWidth="1"/>
-    <col min="4" max="4" width="26" customWidth="1"/>
+    <col min="4" max="4" width="65" customWidth="1"/>
     <col min="5" max="5" width="80" customWidth="1"/>
     <col min="6" max="6" width="27" customWidth="1"/>
     <col min="7" max="7" width="17" customWidth="1"/>
@@ -899,6 +997,190 @@
       </c>
       <c r="G4" s="6" t="s">
         <v>26</v>
+      </c>
+    </row>
+    <row r="5" ht="50" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>1</v>
+      </c>
+      <c r="B5" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="E5" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="F5" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="G5" s="7" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="6" ht="50" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>1</v>
+      </c>
+      <c r="B6" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="E6" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="F6" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="G6" s="7" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="7" ht="50" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>1</v>
+      </c>
+      <c r="B7" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="E7" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="F7" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="G7" s="7" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="8" ht="65" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>1</v>
+      </c>
+      <c r="B8" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="D8" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="E8" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="F8" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="G8" s="7" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="9" ht="65" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>1</v>
+      </c>
+      <c r="B9" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="D9" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="E9" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="F9" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="G9" s="7" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="10" ht="65" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>1</v>
+      </c>
+      <c r="B10" s="5" t="s">
+        <v>51</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="D10" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="E10" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="F10" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="G10" s="7" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="11" ht="50" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>1</v>
+      </c>
+      <c r="B11" s="5" t="s">
+        <v>54</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="D11" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="E11" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="F11" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="G11" s="7" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="12" ht="50" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>1</v>
+      </c>
+      <c r="B12" s="5" t="s">
+        <v>57</v>
+      </c>
+      <c r="C12" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="D12" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="E12" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="F12" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="G12" s="7" t="s">
+        <v>37</v>
       </c>
     </row>
   </sheetData>
@@ -919,24 +1201,24 @@
     <row r="2" spans="1:13" x14ac:dyDescent="0.25"/>
     <row r="3" spans="1:13" x14ac:dyDescent="0.25"/>
     <row r="4" ht="20" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A4" s="7" t="s">
-        <v>1</v>
-      </c>
-      <c r="B4" s="7" t="s">
+      <c r="A4" s="8" t="s">
+        <v>1</v>
+      </c>
+      <c r="B4" s="8" t="s">
         <v>1</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>34</v>
+        <v>60</v>
       </c>
       <c r="D4" s="2"/>
       <c r="E4" s="2"/>
       <c r="F4" s="2"/>
       <c r="G4" s="2"/>
       <c r="H4" s="2" t="s">
-        <v>35</v>
+        <v>61</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>36</v>
+        <v>62</v>
       </c>
       <c r="J4" s="2"/>
       <c r="K4" s="2"/>
@@ -948,40 +1230,40 @@
         <v>1</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>37</v>
+        <v>63</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>38</v>
+        <v>64</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>39</v>
+        <v>65</v>
       </c>
       <c r="E5" s="4" t="s">
-        <v>40</v>
+        <v>66</v>
       </c>
       <c r="F5" s="4" t="s">
-        <v>41</v>
+        <v>67</v>
       </c>
       <c r="G5" s="4" t="s">
-        <v>42</v>
+        <v>68</v>
       </c>
       <c r="H5" s="4" t="s">
-        <v>43</v>
+        <v>69</v>
       </c>
       <c r="I5" s="4" t="s">
-        <v>44</v>
+        <v>70</v>
       </c>
       <c r="J5" s="4" t="s">
-        <v>38</v>
+        <v>64</v>
       </c>
       <c r="K5" s="4" t="s">
-        <v>39</v>
+        <v>65</v>
       </c>
       <c r="L5" s="4" t="s">
-        <v>40</v>
+        <v>66</v>
       </c>
       <c r="M5" s="4" t="s">
-        <v>41</v>
+        <v>67</v>
       </c>
     </row>
     <row r="6" ht="20" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
@@ -989,40 +1271,40 @@
         <v>1</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>45</v>
+        <v>71</v>
       </c>
       <c r="C6" s="1">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="D6" s="1">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="E6" s="1">
         <v>0</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>46</v>
+        <v>72</v>
       </c>
       <c r="G6" s="1">
         <v>0</v>
       </c>
       <c r="H6" s="1" t="s">
-        <v>46</v>
+        <v>72</v>
       </c>
       <c r="I6" s="1" t="s">
-        <v>47</v>
+        <v>73</v>
       </c>
       <c r="J6" s="1">
         <v>0</v>
       </c>
       <c r="K6" s="1" t="s">
-        <v>48</v>
+        <v>74</v>
       </c>
       <c r="L6" s="1" t="s">
-        <v>48</v>
+        <v>74</v>
       </c>
       <c r="M6" s="1" t="s">
-        <v>48</v>
+        <v>74</v>
       </c>
     </row>
   </sheetData>
